--- a/Data/EC/NIT-9009383962.xlsx
+++ b/Data/EC/NIT-9009383962.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B950EE88-A5A9-4522-8F0D-E95AD6B49A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2E11003-BCDA-49D7-89C2-0EF074D5ED43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A9A9734D-117C-450B-82AF-468732395000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F1A36107-E08A-4A98-AAAD-795271A2C23A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="117">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -74,16 +74,19 @@
     <t>YEFRY ENRIQUE OTERO SIMANCAS</t>
   </si>
   <si>
+    <t>2607</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>73009617</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS PUCHE IZQUIERDO</t>
+  </si>
+  <si>
     <t>2606</t>
-  </si>
-  <si>
-    <t>1607</t>
-  </si>
-  <si>
-    <t>73009617</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS PUCHE IZQUIERDO</t>
   </si>
   <si>
     <t>2605</t>
@@ -752,22 +755,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F1DAB5A-4953-9741-D023-2BE025BD85C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD813F2F-271B-D4C6-4F83-E7C40E842374}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -776,7 +779,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -789,7 +792,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1118,27 +1121,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DE5AB4-76BA-40A6-A92E-748BD1CD6397}">
-  <dimension ref="B2:J114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A1D4456-A703-4A60-874A-FCD1C8F62DB8}">
+  <dimension ref="B2:J115"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1147,7 +1150,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1158,7 +1161,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1169,7 +1172,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1180,10 +1183,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1196,8 +1199,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1212,15 +1215,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2985696</v>
+        <v>3016945</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1228,27 +1231,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="5">
         <v>2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F13" s="5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1268,16 +1271,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>110</v>
-      </c>
       <c r="J15" s="14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1300,7 +1303,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1323,7 +1326,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1346,7 +1349,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1369,7 +1372,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1392,7 +1395,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1415,7 +1418,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1438,7 +1441,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1461,7 +1464,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1484,7 +1487,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1507,7 +1510,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1530,7 +1533,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1553,7 +1556,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1576,7 +1579,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1599,7 +1602,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1622,7 +1625,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1645,7 +1648,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1668,7 +1671,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1691,7 +1694,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1714,7 +1717,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1737,7 +1740,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1763,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1783,7 +1786,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1806,7 +1809,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1829,7 +1832,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1852,7 +1855,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1875,7 +1878,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1898,7 +1901,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1921,7 +1924,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1944,7 +1947,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1967,7 +1970,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1990,7 +1993,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2013,7 +2016,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2039,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2059,7 +2062,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2082,7 +2085,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2105,7 +2108,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2128,7 +2131,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2151,7 +2154,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2174,7 +2177,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2200,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2220,7 +2223,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2243,7 +2246,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2266,7 +2269,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2289,7 +2292,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2315,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2338,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2358,7 +2361,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2381,7 +2384,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2404,7 +2407,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2427,7 +2430,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2450,7 +2453,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2473,7 +2476,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2496,7 +2499,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2519,7 +2522,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2542,7 +2545,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2565,7 +2568,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2588,7 +2591,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2611,7 +2614,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2634,7 +2637,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2657,7 +2660,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2680,7 +2683,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2703,7 +2706,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2726,7 +2729,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2749,7 +2752,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2772,7 +2775,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2795,7 +2798,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2818,7 +2821,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2841,7 +2844,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2864,7 +2867,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2887,7 +2890,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2910,7 +2913,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2933,7 +2936,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2956,7 +2959,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2979,7 +2982,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3002,7 +3005,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3025,7 +3028,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3048,7 +3051,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3071,7 +3074,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3094,7 +3097,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3117,7 +3120,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3140,7 +3143,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3163,7 +3166,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3186,7 +3189,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3209,7 +3212,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3232,7 +3235,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3255,7 +3258,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3278,7 +3281,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3301,7 +3304,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3324,7 +3327,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3347,7 +3350,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3370,7 +3373,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3393,43 +3396,55 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B108" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D108" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E108" s="22" t="s">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B108" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="F108" s="24">
-        <v>31249</v>
-      </c>
-      <c r="G108" s="24">
-        <v>781242</v>
-      </c>
-      <c r="H108" s="25"/>
-      <c r="I108" s="25"/>
-      <c r="J108" s="26"/>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B113" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C113" s="32"/>
-      <c r="H113" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="F108" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G108" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="20"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B109" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F109" s="24">
+        <v>31249</v>
+      </c>
+      <c r="G109" s="24">
+        <v>781242</v>
+      </c>
+      <c r="H109" s="25"/>
+      <c r="I109" s="25"/>
+      <c r="J109" s="26"/>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C114" s="32"/>
       <c r="H114" s="1" t="s">
@@ -3438,12 +3453,23 @@
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
     </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B115" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C115" s="32"/>
+      <c r="H115" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B115:C115"/>
     <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="H115:J115"/>
     <mergeCell ref="H114:J114"/>
-    <mergeCell ref="H113:J113"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
